--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46015.33333333334</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,76 +659,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46015.33333333334</v>
+        <v>46015.29166666666</v>
       </c>
     </row>
     <row r="3">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46015.375</v>
+        <v>46015.33333333334</v>
       </c>
     </row>
     <row r="5">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46015.38541666666</v>
+        <v>46015.375</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46015.41666666666</v>
+        <v>46015.38541666666</v>
       </c>
     </row>
     <row r="8">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46015.5</v>
+        <v>46015.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1808,116 +1808,235 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Adama Kenema</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mekelakeya</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>46015.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Algeria Ligue 1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>CR Belouizdad</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>ES Sétif</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>1.52</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>3.55</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N13" t="n">
         <v>5.8</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.14</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AB13" t="n">
         <v>1.61</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46015.875</v>
       </c>
     </row>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>5.18</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
@@ -942,10 +942,10 @@
         <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
         <v>3.42</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,125 +1918,6 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46015.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46015</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3" t="n">
         <v>46015.875</v>
       </c>
     </row>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1800,125 +1800,6 @@
       </c>
       <c r="AI11" s="3" t="n">
         <v>46015.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46015</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3" t="n">
-        <v>46015.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -781,10 +781,10 @@
         <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
         <v>2.1</v>
@@ -793,19 +793,19 @@
         <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.13</v>
+        <v>5.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
         <v>5.75</v>
@@ -820,13 +820,13 @@
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
         <v>3.75</v>
@@ -835,13 +835,13 @@
         <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
         <v>2.71</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
         <v>2.3</v>
@@ -1165,7 +1165,7 @@
         <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1177,13 +1177,13 @@
         <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
         <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
         <v>2.75</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.33</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.74</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.88</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.74</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
         <v>2.3</v>
@@ -900,10 +900,10 @@
         <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
@@ -942,10 +942,10 @@
         <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
         <v>3.75</v>
@@ -1025,19 +1025,19 @@
         <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
         <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
@@ -1064,13 +1064,13 @@
         <v>1.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
         <v>2.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
         <v>1.75</v>
@@ -1079,10 +1079,10 @@
         <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -832,7 +832,7 @@
         <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1025,19 +1025,19 @@
         <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
         <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
@@ -1046,7 +1046,7 @@
         <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.09</v>
@@ -1055,22 +1055,22 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.57</v>
+        <v>4.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
         <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
         <v>1.75</v>
@@ -1079,10 +1079,10 @@
         <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
         <v>2.66</v>
       </c>
       <c r="N10" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
         <v>2.3</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.66</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
         <v>5.13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
         <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V4" t="n">
         <v>5.75</v>
@@ -936,16 +936,16 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
         <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
         <v>3.75</v>
@@ -954,7 +954,7 @@
         <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
         <v>1.7</v>
@@ -1028,16 +1028,16 @@
         <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.25</v>
+        <v>6.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
@@ -1055,25 +1055,25 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>2</v>
@@ -1082,7 +1082,7 @@
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.7</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>4.45</v>
+        <v>4.66</v>
       </c>
       <c r="N3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.36</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>4.66</v>
+        <v>4.45</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>1.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
         <v>3.5</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.66</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="P3" t="n">
         <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.13</v>
+        <v>4.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
         <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
         <v>1.06</v>
@@ -820,16 +820,16 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
         <v>1.36</v>
@@ -838,10 +838,10 @@
         <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
         <v>2.71</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
         <v>2.3</v>
@@ -1028,28 +1028,28 @@
         <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.36</v>
+        <v>6.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -787,22 +787,22 @@
         <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.95</v>
+        <v>5.93</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U3" t="n">
         <v>1.43</v>
@@ -811,16 +811,16 @@
         <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
         <v>1.87</v>
@@ -844,7 +844,7 @@
         <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -906,13 +906,13 @@
         <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1025,52 +1025,52 @@
         <v>6.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="T5" t="n">
         <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
         <v>5.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
         <v>1.7</v>
@@ -1082,7 +1082,7 @@
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.01</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.93</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.33</v>
       </c>
-      <c r="O4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>6.72</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.75</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>3.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46015.29166666666</v>
@@ -906,25 +906,25 @@
         <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.93</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.27</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V4" t="n">
         <v>5.75</v>
@@ -936,10 +936,10 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
         <v>1.87</v>
@@ -948,22 +948,22 @@
         <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1144,28 +1144,28 @@
         <v>6.72</v>
       </c>
       <c r="O6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1183,22 +1183,22 @@
         <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
         <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
         <v>2.4</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.46</v>
+        <v>4.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
         <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.98</v>
+        <v>3.11</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="N11" t="n">
-        <v>4.03</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
         <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46015.5</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>5.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
         <v>5.5</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -900,16 +900,16 @@
         <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
         <v>5.5</v>
@@ -918,16 +918,16 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
         <v>1.48</v>
       </c>
       <c r="V4" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>
@@ -939,19 +939,19 @@
         <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
         <v>1.81</v>
@@ -963,7 +963,7 @@
         <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>2.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
       <c r="N6" t="n">
-        <v>6.72</v>
+        <v>6.64</v>
       </c>
       <c r="O6" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1165,7 +1165,7 @@
         <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1174,7 +1174,7 @@
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
         <v>3.9</v>
@@ -1186,13 +1186,13 @@
         <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
         <v>2</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46015.38541666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.45</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.55</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.63</v>
+        <v>2.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.06</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.07</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.32</v>
+        <v>2.43</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="M2" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>3.01</v>
@@ -698,16 +698,16 @@
         <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AC2" t="n">
         <v>6.3</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
@@ -1055,16 +1055,16 @@
         <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
         <v>5.8</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.63</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.06</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.07</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>2.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.84</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.85</v>
+        <v>4.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.9</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.1</v>
+        <v>1.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>3.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>6.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.66</v>
+        <v>1.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.02</v>
+        <v>2.84</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
         <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
         <v>1.62</v>
@@ -1650,34 +1650,34 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
         <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AG10" t="n">
         <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>4.2</v>
@@ -1769,16 +1769,16 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
         <v>6.1</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
         <v>5.5</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -900,13 +900,13 @@
         <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="P4" t="n">
         <v>2.35</v>
@@ -915,7 +915,7 @@
         <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
         <v>2.65</v>
@@ -924,7 +924,7 @@
         <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
         <v>5.8</v>
@@ -936,16 +936,16 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
         <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
         <v>3.75</v>
@@ -960,7 +960,7 @@
         <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
         <v>2.49</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>4.61</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>6.64</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>2.11</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>3.92</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>4.61</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>6.64</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.9</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>3.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.09</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>2.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
         <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
@@ -1278,10 +1278,10 @@
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
         <v>5.3</v>
@@ -1296,16 +1296,16 @@
         <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
@@ -1317,10 +1317,10 @@
         <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46015.38541666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
         <v>3.9</v>
@@ -1412,16 +1412,16 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AC8" t="n">
         <v>2.2</v>
@@ -1430,16 +1430,16 @@
         <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AG8" t="n">
         <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.2</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.84</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>4.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.9</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.68</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>6.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.66</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>13</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA8" t="n">
         <v>3.04</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.46</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
         <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
         <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
         <v>1.18</v>
@@ -1531,16 +1531,16 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC9" t="n">
         <v>2.2</v>
@@ -1549,16 +1549,16 @@
         <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AG9" t="n">
         <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="M10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>13</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -668,28 +668,28 @@
         <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.18</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="T2" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -710,22 +710,22 @@
         <v>1.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="AD2" t="n">
         <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46015.29166666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.33</v>
       </c>
-      <c r="O3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1019,16 +1019,16 @@
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="N5" t="n">
-        <v>6.64</v>
+        <v>6.71</v>
       </c>
       <c r="O5" t="n">
         <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
         <v>6</v>
@@ -1043,13 +1043,13 @@
         <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
         <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1067,7 +1067,7 @@
         <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
@@ -1076,13 +1076,13 @@
         <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
         <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1144,19 +1144,19 @@
         <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
         <v>3.92</v>
@@ -1165,13 +1165,13 @@
         <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.65</v>
@@ -1186,22 +1186,22 @@
         <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1263,40 +1263,40 @@
         <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA7" t="n">
         <v>1.7</v>
@@ -1305,22 +1305,22 @@
         <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46015.38541666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.2</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
         <v>1.18</v>
@@ -1531,16 +1531,16 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
         <v>2.2</v>
@@ -1549,16 +1549,16 @@
         <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AG9" t="n">
         <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.94</v>
+        <v>4.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>2.03</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1739,40 +1739,40 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.24</v>
+        <v>4.18</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="U11" t="n">
         <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
         <v>2.99</v>
@@ -1781,22 +1781,22 @@
         <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46015.5</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.09</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.33</v>
       </c>
-      <c r="O4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>4.63</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>6.71</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>3.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>2.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.86</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>4.63</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>6.71</v>
       </c>
       <c r="O6" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>3.92</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.4</v>
+        <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.48</v>
+        <v>2.86</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="N3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.33</v>
       </c>
-      <c r="O3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.09</v>
+        <v>5.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>4.63</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>6.71</v>
       </c>
       <c r="O5" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>3.92</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>2.86</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>4.63</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>6.71</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>3.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>2.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.57</v>
+        <v>5.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.86</v>
+        <v>1.48</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,55 +1373,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
         <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC8" t="n">
         <v>2.2</v>
@@ -1430,16 +1430,16 @@
         <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AG8" t="n">
         <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,70 +1492,70 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.96</v>
+        <v>4.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>2.03</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.47</v>
+        <v>3.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.59</v>
+        <v>1.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
         <v>1.48</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="M10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V10" t="n">
-        <v>13</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -642,48 +642,48 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
         <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U2" t="n">
         <v>1.17</v>
@@ -698,34 +698,34 @@
         <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
         <v>5.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46015.29166666666</v>
@@ -778,37 +778,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.93</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
         <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
         <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
@@ -823,28 +823,28 @@
         <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
         <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
         <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,17 +893,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
         <v>5.5</v>
@@ -942,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
         <v>1.83</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.63</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>6.71</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>4.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>3.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>2.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.86</v>
+        <v>1.54</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>4.55</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.14</v>
+        <v>1.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>3.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.48</v>
+        <v>2.89</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
         <v>5.8</v>
@@ -1296,31 +1296,31 @@
         <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46015.38541666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>2.69</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>3.46</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.96</v>
+        <v>4.74</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>2.06</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.47</v>
+        <v>3.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>6.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.59</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.68</v>
+        <v>3.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.02</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.04</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.46</v>
+        <v>2.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1611,61 +1611,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
         <v>1.42</v>
@@ -1674,10 +1674,10 @@
         <v>2.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.18</v>
+        <v>4.47</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
         <v>3.96</v>
@@ -1766,37 +1766,37 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="AD11" t="n">
         <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
         <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46015.5</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,19 +752,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O3" t="n">
         <v>5.5</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.05</v>
-      </c>
       <c r="P3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,23 +871,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="P4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>4.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>1.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.32</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>3.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>9.4</v>
+        <v>5.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.21</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.54</v>
+        <v>2.89</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>4.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>3.23</v>
+        <v>2.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.55</v>
       </c>
-      <c r="V6" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.89</v>
+        <v>1.54</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1237,20 +1237,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="M8" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>3.46</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.04</v>
+        <v>1.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>3.46</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.02</v>
+        <v>4.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>2.06</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>6.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.45</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
         <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AG10" t="n">
         <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="M11" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1769,16 +1769,16 @@
         <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
         <v>5.85</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>4.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>3.23</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="U5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.55</v>
       </c>
-      <c r="V5" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.89</v>
+        <v>1.54</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>4.55</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.96</v>
+        <v>1.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.32</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>2.18</v>
+        <v>3.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.21</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.54</v>
+        <v>2.89</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>3.46</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>3.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>4.74</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.49</v>
+        <v>3.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.27</v>
+        <v>6.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="M9" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.46</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.04</v>
+        <v>1.49</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1597,17 +1597,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,90 +1713,90 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>2.46</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.47</v>
+        <v>4.18</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="T11" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="AB11" t="n">
         <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46015.5</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,23 +752,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,22 +871,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O4" t="n">
         <v>5.5</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>3.46</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.74</v>
+        <v>3.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.04</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>2.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,25 +1585,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>3.46</v>
       </c>
       <c r="O10" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.02</v>
+        <v>4.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.5</v>
+        <v>2.06</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.28</v>
+        <v>6.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.45</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>

--- a/jogos_2025-12-24.xlsx
+++ b/jogos_2025-12-24.xlsx
@@ -752,22 +752,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O3" t="n">
         <v>5.5</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.05</v>
-      </c>
       <c r="P3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46015.33333333334</v>
@@ -871,23 +871,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="P4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46015.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>4.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>1.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.32</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>3.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>9.4</v>
+        <v>5.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.21</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.54</v>
+        <v>2.89</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46015.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>4.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>3.23</v>
+        <v>2.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.55</v>
       </c>
-      <c r="V6" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.89</v>
+        <v>1.54</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46015.375</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,25 +1466,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>3.46</v>
       </c>
       <c r="O9" t="n">
-        <v>2.54</v>
+        <v>3.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>4.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.49</v>
+        <v>3.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.27</v>
+        <v>6.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46015.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,25 +1585,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="M10" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.46</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.74</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>4.15</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.04</v>
+        <v>1.49</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46015.41666666666</v>
